--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.66407453796224</v>
+        <v>10.02041211241887</v>
       </c>
       <c r="D2" t="n">
-        <v>19.29378138157474</v>
+        <v>3.135239474505895</v>
       </c>
       <c r="E2" t="n">
-        <v>7.083221598829927</v>
+        <v>1.151023509809863</v>
       </c>
       <c r="F2" t="n">
-        <v>17.69198829251224</v>
+        <v>2.874948097533239</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>74.30478804945758</v>
+        <v>12.07452805803686</v>
       </c>
       <c r="D3" t="n">
-        <v>17.86756838520564</v>
+        <v>2.903479862595916</v>
       </c>
       <c r="E3" t="n">
-        <v>7.083221598829927</v>
+        <v>1.151023509809863</v>
       </c>
       <c r="F3" t="n">
-        <v>17.69198829251224</v>
+        <v>2.874948097533239</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.40275409318713</v>
+        <v>9.815447540142909</v>
       </c>
       <c r="D4" t="n">
-        <v>31.84729187858836</v>
+        <v>5.175184930270608</v>
       </c>
       <c r="E4" t="n">
-        <v>7.083221598829927</v>
+        <v>1.151023509809863</v>
       </c>
       <c r="F4" t="n">
-        <v>17.69198829251224</v>
+        <v>2.874948097533239</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.80672148825544</v>
+        <v>9.39359224184151</v>
       </c>
       <c r="D5" t="n">
-        <v>56.83177791253469</v>
+        <v>9.235163910786888</v>
       </c>
       <c r="E5" t="n">
-        <v>7.083221598829927</v>
+        <v>1.151023509809863</v>
       </c>
       <c r="F5" t="n">
-        <v>17.69198829251224</v>
+        <v>2.874948097533239</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>54.23991488826628</v>
+        <v>8.81398616934327</v>
       </c>
       <c r="D6" t="n">
-        <v>19.79898987322333</v>
+        <v>3.217335854398792</v>
       </c>
       <c r="E6" t="n">
-        <v>7.083221598829927</v>
+        <v>1.151023509809863</v>
       </c>
       <c r="F6" t="n">
-        <v>17.69198829251224</v>
+        <v>2.874948097533239</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>73.44831697038636</v>
+        <v>11.93535150768778</v>
       </c>
       <c r="D7" t="n">
-        <v>66.99635051854345</v>
+        <v>10.88690695926331</v>
       </c>
       <c r="E7" t="n">
-        <v>7.083221598829927</v>
+        <v>1.151023509809863</v>
       </c>
       <c r="F7" t="n">
-        <v>17.69198829251224</v>
+        <v>2.874948097533239</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>71.1329242088367</v>
+        <v>11.55910018393596</v>
       </c>
       <c r="D8" t="n">
-        <v>49.26863736247995</v>
+        <v>8.006153571402992</v>
       </c>
       <c r="E8" t="n">
-        <v>7.083221598829927</v>
+        <v>1.151023509809863</v>
       </c>
       <c r="F8" t="n">
-        <v>17.69198829251224</v>
+        <v>2.874948097533239</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>67.45986722404216</v>
+        <v>10.96222842390685</v>
       </c>
       <c r="D9" t="n">
-        <v>29.15682814634602</v>
+        <v>4.737984573781228</v>
       </c>
       <c r="E9" t="n">
-        <v>7.083221598829927</v>
+        <v>1.151023509809863</v>
       </c>
       <c r="F9" t="n">
-        <v>17.69198829251224</v>
+        <v>2.874948097533239</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
